--- a/ocean monument.xlsx
+++ b/ocean monument.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\friend-zone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE31661-6F10-44B7-8E73-F0A28FC55B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E74C3B-B1CC-2C4E-BCFA-14A80BDC78DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="795" windowWidth="7455" windowHeight="16095" xr2:uid="{07D44569-79BD-4F9D-B81C-4BABD9EEFACF}"/>
+    <workbookView xWindow="40" yWindow="500" windowWidth="33600" windowHeight="19120" xr2:uid="{07D44569-79BD-4F9D-B81C-4BABD9EEFACF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,227 +34,20 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>/tp -280 ~ -6040</t>
+    <t>nummer</t>
   </si>
   <si>
-    <t>/tp 56 ~ -6040</t>
+    <t>X</t>
   </si>
   <si>
-    <t>/tp 3784 ~ -4344</t>
-  </si>
-  <si>
-    <t>/tp 232 ~ -2840</t>
-  </si>
-  <si>
-    <t>/tp 616 ~ -2248</t>
-  </si>
-  <si>
-    <t>/tp 344 ~ -2152</t>
-  </si>
-  <si>
-    <t>/tp 600 ~ -1736</t>
-  </si>
-  <si>
-    <t>/tp 296 ~ -1720</t>
-  </si>
-  <si>
-    <t>/tp -376 ~ -1864</t>
-  </si>
-  <si>
-    <t>/tp 1304 ~ -2232</t>
-  </si>
-  <si>
-    <t>/tp 2728 ~ -1800</t>
-  </si>
-  <si>
-    <t>/tp 1112 ~ -1672</t>
-  </si>
-  <si>
-    <t>/tp 1112 ~ -1432</t>
-  </si>
-  <si>
-    <t>/tp 1352 ~ -872</t>
-  </si>
-  <si>
-    <t>/tp 1560 ~ -824</t>
-  </si>
-  <si>
-    <t>/tp 648 ~ -888</t>
-  </si>
-  <si>
-    <t>/tp 296 ~ -792</t>
-  </si>
-  <si>
-    <t>/tp 920 ~ -1336</t>
-  </si>
-  <si>
-    <t>/tp 248 ~ -1368</t>
-  </si>
-  <si>
-    <t>/tp 5880 ~ -1208</t>
-  </si>
-  <si>
-    <t>/tp 5736 ~ -744</t>
-  </si>
-  <si>
-    <t>/tp 5336 ~ -648</t>
-  </si>
-  <si>
-    <t>/tp 5800 ~ -376</t>
-  </si>
-  <si>
-    <t>/tp 1752 ~ -312</t>
-  </si>
-  <si>
-    <t>/tp 1272 ~ -200</t>
-  </si>
-  <si>
-    <t>/tp 1224 ~ 248</t>
-  </si>
-  <si>
-    <t>/tp 712 ~ 776</t>
-  </si>
-  <si>
-    <t>/tp 328 ~ 1128</t>
-  </si>
-  <si>
-    <t>/tp 1624 ~ 648</t>
-  </si>
-  <si>
-    <t>/tp 1672 ~ 1320</t>
-  </si>
-  <si>
-    <t>/tp 2744 ~ 1288</t>
-  </si>
-  <si>
-    <t>/tp 3320 ~ 1336</t>
-  </si>
-  <si>
-    <t>/tp 5272 ~ 1800</t>
-  </si>
-  <si>
-    <t>/tp 4296 ~ 1784</t>
-  </si>
-  <si>
-    <t>/tp 3832 ~ 1784</t>
-  </si>
-  <si>
-    <t>/tp 2664 ~ 1784</t>
-  </si>
-  <si>
-    <t>/tp 3656 ~ 3416</t>
-  </si>
-  <si>
-    <t>/tp 3864 ~ 2328</t>
-  </si>
-  <si>
-    <t>/tp 5912 ~ 5256</t>
-  </si>
-  <si>
-    <t>/tp 3640 ~ 5240</t>
-  </si>
-  <si>
-    <t>/tp 2712 ~ 5288</t>
-  </si>
-  <si>
-    <t>/tp 2216 ~ 5416</t>
-  </si>
-  <si>
-    <t>/tp 1656 ~ 5848</t>
-  </si>
-  <si>
-    <t>/tp 1304 ~ 5960</t>
-  </si>
-  <si>
-    <t>/tp 2360 ~ 5944</t>
-  </si>
-  <si>
-    <t>/tp 1176 ~ 5400</t>
-  </si>
-  <si>
-    <t>/tp 1800 ~ 5256</t>
-  </si>
-  <si>
-    <t>/tp 1880 ~ 4712</t>
-  </si>
-  <si>
-    <t>/tp -1480 ~ 5784</t>
-  </si>
-  <si>
-    <t>/tp -2488 ~ 4888</t>
-  </si>
-  <si>
-    <t>/tp -1800 ~ 4792</t>
-  </si>
-  <si>
-    <t>/tp -2280 ~ 4392</t>
-  </si>
-  <si>
-    <t>/tp -1912 ~ 4264</t>
-  </si>
-  <si>
-    <t>/tp -1368 ~ 3768</t>
-  </si>
-  <si>
-    <t>/tp -1752 ~ 3688</t>
-  </si>
-  <si>
-    <t>/tp -3288 ~ 3384</t>
-  </si>
-  <si>
-    <t>/tp -3416 ~ 3816</t>
-  </si>
-  <si>
-    <t>/tp -1752 ~ 3240</t>
-  </si>
-  <si>
-    <t>/tp -2312 ~ 2696</t>
-  </si>
-  <si>
-    <t>/tp -1912 ~ 2760</t>
-  </si>
-  <si>
-    <t>/tp -1864 ~ 1848</t>
-  </si>
-  <si>
-    <t>/tp -2328 ~ 2264</t>
-  </si>
-  <si>
-    <t>/tp -1960 ~ 2360</t>
-  </si>
-  <si>
-    <t>/tp -3768 ~ -376</t>
-  </si>
-  <si>
-    <t>/tp -2456 ~ -1256</t>
-  </si>
-  <si>
-    <t>/tp -5976 ~ 1704</t>
-  </si>
-  <si>
-    <t>/tp -2472 ~ -2856</t>
-  </si>
-  <si>
-    <t>/tp -4824 ~ -4360</t>
-  </si>
-  <si>
-    <t>/tp -4312 ~ -5384</t>
-  </si>
-  <si>
-    <t>/tp -4936 ~ -5432</t>
-  </si>
-  <si>
-    <t>/tp -3944 ~ -5912</t>
+    <t>Z</t>
   </si>
 </sst>
 </file>
@@ -623,365 +419,807 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15958F6C-D0C3-4305-981B-73D19B23D0A4}">
-  <dimension ref="A1:A71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C72"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5912</v>
+      </c>
+      <c r="C2">
+        <v>5256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5880</v>
+      </c>
+      <c r="C3">
+        <v>-1208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4">
+        <v>5800</v>
+      </c>
+      <c r="C4">
+        <v>-376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B5">
+        <v>5736</v>
+      </c>
+      <c r="C5">
+        <v>-744</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6">
+        <v>5336</v>
+      </c>
+      <c r="C6">
+        <v>-648</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7">
+        <v>5272</v>
+      </c>
+      <c r="C7">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8">
+        <v>4296</v>
+      </c>
+      <c r="C8">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9">
+        <v>3864</v>
+      </c>
+      <c r="C9">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10">
+        <v>3832</v>
+      </c>
+      <c r="C10">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11">
+        <v>3784</v>
+      </c>
+      <c r="C11">
+        <v>-4344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12">
+        <v>3656</v>
+      </c>
+      <c r="C12">
+        <v>3416</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B13">
+        <v>3640</v>
+      </c>
+      <c r="C13">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B14">
+        <v>3320</v>
+      </c>
+      <c r="C14">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B15">
+        <v>2744</v>
+      </c>
+      <c r="C15">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B16">
+        <v>2728</v>
+      </c>
+      <c r="C16">
+        <v>-1800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B17">
+        <v>2712</v>
+      </c>
+      <c r="C17">
+        <v>5288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B18">
+        <v>2664</v>
+      </c>
+      <c r="C18">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B19">
+        <v>2360</v>
+      </c>
+      <c r="C19">
+        <v>5944</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B20">
+        <v>2216</v>
+      </c>
+      <c r="C20">
+        <v>5416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B21">
+        <v>1880</v>
+      </c>
+      <c r="C21">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B22">
+        <v>1800</v>
+      </c>
+      <c r="C22">
+        <v>5256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B23">
+        <v>1752</v>
+      </c>
+      <c r="C23">
+        <v>-312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B24">
+        <v>1672</v>
+      </c>
+      <c r="C24">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B25">
+        <v>1656</v>
+      </c>
+      <c r="C25">
+        <v>5848</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B26">
+        <v>1624</v>
+      </c>
+      <c r="C26">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B27">
+        <v>1560</v>
+      </c>
+      <c r="C27">
+        <v>-824</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B28">
+        <v>1352</v>
+      </c>
+      <c r="C28">
+        <v>-872</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29">
+        <v>1304</v>
+      </c>
+      <c r="C29">
+        <v>-2232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B30">
+        <v>1304</v>
+      </c>
+      <c r="C30">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B31">
+        <v>1272</v>
+      </c>
+      <c r="C31">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B32">
+        <v>1224</v>
+      </c>
+      <c r="C32">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B33">
+        <v>1176</v>
+      </c>
+      <c r="C33">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B34">
+        <v>1112</v>
+      </c>
+      <c r="C34">
+        <v>-1672</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B35">
+        <v>1112</v>
+      </c>
+      <c r="C35">
+        <v>-1432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B36">
+        <v>920</v>
+      </c>
+      <c r="C36">
+        <v>-1336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B37">
+        <v>712</v>
+      </c>
+      <c r="C37">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B38">
+        <v>648</v>
+      </c>
+      <c r="C38">
+        <v>-888</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B39">
+        <v>616</v>
+      </c>
+      <c r="C39">
+        <v>-2248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B40">
+        <v>600</v>
+      </c>
+      <c r="C40">
+        <v>-1736</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B41">
+        <v>344</v>
+      </c>
+      <c r="C41">
+        <v>-2152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B42">
+        <v>328</v>
+      </c>
+      <c r="C42">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B43">
+        <v>296</v>
+      </c>
+      <c r="C43">
+        <v>-1720</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B44">
+        <v>296</v>
+      </c>
+      <c r="C44">
+        <v>-792</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="B45">
+        <v>248</v>
+      </c>
+      <c r="C45">
+        <v>-1368</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B46">
+        <v>232</v>
+      </c>
+      <c r="C46">
+        <v>-2840</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B47">
+        <v>56</v>
+      </c>
+      <c r="C47">
+        <v>-6040</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B48">
+        <v>-280</v>
+      </c>
+      <c r="C48">
+        <v>-6040</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B49">
+        <v>-376</v>
+      </c>
+      <c r="C49">
+        <v>-1864</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B50">
+        <v>-1368</v>
+      </c>
+      <c r="C50">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B51">
+        <v>-1480</v>
+      </c>
+      <c r="C51">
+        <v>5784</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B52">
+        <v>-1752</v>
+      </c>
+      <c r="C52">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B53">
+        <v>-1752</v>
+      </c>
+      <c r="C53">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B54">
+        <v>-1800</v>
+      </c>
+      <c r="C54">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B55">
+        <v>-1864</v>
+      </c>
+      <c r="C55">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B56">
+        <v>-1912</v>
+      </c>
+      <c r="C56">
+        <v>4264</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B57">
+        <v>-1912</v>
+      </c>
+      <c r="C57">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B58">
+        <v>-1960</v>
+      </c>
+      <c r="C58">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B59">
+        <v>-2280</v>
+      </c>
+      <c r="C59">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B60">
+        <v>-2312</v>
+      </c>
+      <c r="C60">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B61">
+        <v>-2328</v>
+      </c>
+      <c r="C61">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B62">
+        <v>-2456</v>
+      </c>
+      <c r="C62">
+        <v>-1256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B63">
+        <v>-2472</v>
+      </c>
+      <c r="C63">
+        <v>-2856</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B64">
+        <v>-2488</v>
+      </c>
+      <c r="C64">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B65">
+        <v>-3288</v>
+      </c>
+      <c r="C65">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B66">
+        <v>-3416</v>
+      </c>
+      <c r="C66">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B67">
+        <v>-3768</v>
+      </c>
+      <c r="C67">
+        <v>-376</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B68">
+        <v>-3944</v>
+      </c>
+      <c r="C68">
+        <v>-5912</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B69">
+        <v>-4312</v>
+      </c>
+      <c r="C69">
+        <v>-5384</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B70">
+        <v>-4824</v>
+      </c>
+      <c r="C70">
+        <v>-4360</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71">
         <v>70</v>
       </c>
+      <c r="B71">
+        <v>-4936</v>
+      </c>
+      <c r="C71">
+        <v>-5432</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>-5976</v>
+      </c>
+      <c r="C72">
+        <v>1704</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{15958F6C-D0C3-4305-981B-73D19B23D0A4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D72">
+      <sortCondition descending="1" ref="B1:B72"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>